--- a/bonos_flujos.xlsx
+++ b/bonos_flujos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29421"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D9416AD-6BB7-40DA-B64A-322DC4DD91A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C1AAE0-DC83-4CDD-9646-FE92707300F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,7 +129,7 @@
     <t>PAE 2029 7,00%</t>
   </si>
   <si>
-    <t>PN35</t>
+    <t>PN35D</t>
   </si>
   <si>
     <t>PAE 2027 4,97%</t>

--- a/bonos_flujos.xlsx
+++ b/bonos_flujos.xlsx
@@ -1,18 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29421"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6837400F-1F18-48AC-9819-D4BC6CA4A2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64E288F3-120C-4729-9691-2657A1C7CB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="195">
   <si>
     <t>GD29</t>
   </si>
@@ -596,6 +593,30 @@
   <si>
     <t>RC1CD</t>
   </si>
+  <si>
+    <t>TECPETROL 2030 7,625%</t>
+  </si>
+  <si>
+    <t>TTCD</t>
+  </si>
+  <si>
+    <t>PAMPA 2037 7,75%</t>
+  </si>
+  <si>
+    <t>MGCR</t>
+  </si>
+  <si>
+    <t>PLUSPETROL 2031 8,125%</t>
+  </si>
+  <si>
+    <t>PLC5</t>
+  </si>
+  <si>
+    <t>TGS 2035 7,75%</t>
+  </si>
+  <si>
+    <t>TSC4</t>
+  </si>
 </sst>
 </file>
 
@@ -671,19 +692,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Ar"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1003,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:N1352"/>
+  <dimension ref="A2:N1425"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
@@ -23698,9 +23706,1267 @@
         <v>35.29</v>
       </c>
     </row>
+    <row r="1353" spans="1:5">
+      <c r="A1353" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1353">
+        <v>2</v>
+      </c>
+      <c r="D1353" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:5">
+      <c r="A1354" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:5">
+      <c r="A1355" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B1355">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1355">
+        <v>3.8125</v>
+      </c>
+      <c r="D1355">
+        <v>0</v>
+      </c>
+      <c r="E1355">
+        <f>+C1355+D1355</f>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:5">
+      <c r="A1356" s="1">
+        <v>46329</v>
+      </c>
+      <c r="B1356">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1356">
+        <v>3.8125</v>
+      </c>
+      <c r="D1356">
+        <v>0</v>
+      </c>
+      <c r="E1356">
+        <f t="shared" ref="E1356:E1419" si="0">+C1356+D1356</f>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:5">
+      <c r="A1357" s="1">
+        <v>46510</v>
+      </c>
+      <c r="B1357">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1357">
+        <v>3.8125</v>
+      </c>
+      <c r="D1357">
+        <v>0</v>
+      </c>
+      <c r="E1357">
+        <f t="shared" si="0"/>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:5">
+      <c r="A1358" s="1">
+        <v>46694</v>
+      </c>
+      <c r="B1358">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1358">
+        <v>3.8125</v>
+      </c>
+      <c r="D1358">
+        <v>0</v>
+      </c>
+      <c r="E1358">
+        <f t="shared" si="0"/>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:5">
+      <c r="A1359" s="1">
+        <v>46876</v>
+      </c>
+      <c r="B1359">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1359">
+        <v>3.8125</v>
+      </c>
+      <c r="D1359">
+        <v>0</v>
+      </c>
+      <c r="E1359">
+        <f t="shared" si="0"/>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:5">
+      <c r="A1360" s="1">
+        <v>47060</v>
+      </c>
+      <c r="B1360">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1360">
+        <v>3.8125</v>
+      </c>
+      <c r="D1360">
+        <v>0</v>
+      </c>
+      <c r="E1360">
+        <f t="shared" si="0"/>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:5">
+      <c r="A1361" s="1">
+        <v>47241</v>
+      </c>
+      <c r="B1361">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1361">
+        <v>3.8125</v>
+      </c>
+      <c r="D1361">
+        <v>0</v>
+      </c>
+      <c r="E1361">
+        <f t="shared" si="0"/>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:5">
+      <c r="A1362" s="1">
+        <v>47427</v>
+      </c>
+      <c r="B1362">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1362">
+        <v>3.8125</v>
+      </c>
+      <c r="D1362">
+        <v>0</v>
+      </c>
+      <c r="E1362">
+        <f t="shared" si="0"/>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:5">
+      <c r="A1363" s="1">
+        <v>47606</v>
+      </c>
+      <c r="B1363">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1363">
+        <v>3.8125</v>
+      </c>
+      <c r="D1363">
+        <v>0</v>
+      </c>
+      <c r="E1363">
+        <f t="shared" si="0"/>
+        <v>3.8125</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:5">
+      <c r="A1364" s="1">
+        <v>47791</v>
+      </c>
+      <c r="B1364">
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C1364">
+        <v>3.8125</v>
+      </c>
+      <c r="D1364">
+        <v>100</v>
+      </c>
+      <c r="E1364">
+        <f t="shared" si="0"/>
+        <v>103.8125</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:5">
+      <c r="A1365" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1365">
+        <v>2</v>
+      </c>
+      <c r="D1365" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:5">
+      <c r="A1366" s="1">
+        <v>45975</v>
+      </c>
+      <c r="E1366">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:5">
+      <c r="A1367" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1367">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1367">
+        <v>3.875</v>
+      </c>
+      <c r="D1367">
+        <v>0</v>
+      </c>
+      <c r="E1367">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:5">
+      <c r="A1368" s="1">
+        <v>46342</v>
+      </c>
+      <c r="B1368">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1368">
+        <v>3.875</v>
+      </c>
+      <c r="D1368">
+        <v>0</v>
+      </c>
+      <c r="E1368">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:5">
+      <c r="A1369" s="1">
+        <v>46521</v>
+      </c>
+      <c r="B1369">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1369">
+        <v>3.875</v>
+      </c>
+      <c r="D1369">
+        <v>0</v>
+      </c>
+      <c r="E1369">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:5">
+      <c r="A1370" s="1">
+        <v>46706</v>
+      </c>
+      <c r="B1370">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1370">
+        <v>3.875</v>
+      </c>
+      <c r="D1370">
+        <v>0</v>
+      </c>
+      <c r="E1370">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:5">
+      <c r="A1371" s="1">
+        <v>46888</v>
+      </c>
+      <c r="B1371">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1371">
+        <v>3.875</v>
+      </c>
+      <c r="D1371">
+        <v>0</v>
+      </c>
+      <c r="E1371">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:5">
+      <c r="A1372" s="1">
+        <v>47071</v>
+      </c>
+      <c r="B1372">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1372">
+        <v>3.875</v>
+      </c>
+      <c r="D1372">
+        <v>0</v>
+      </c>
+      <c r="E1372">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:5">
+      <c r="A1373" s="1">
+        <v>47252</v>
+      </c>
+      <c r="B1373">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1373">
+        <v>3.875</v>
+      </c>
+      <c r="D1373">
+        <v>0</v>
+      </c>
+      <c r="E1373">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:5">
+      <c r="A1374" s="1">
+        <v>47436</v>
+      </c>
+      <c r="B1374">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1374">
+        <v>3.875</v>
+      </c>
+      <c r="D1374">
+        <v>0</v>
+      </c>
+      <c r="E1374">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:5">
+      <c r="A1375" s="1">
+        <v>47617</v>
+      </c>
+      <c r="B1375">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1375">
+        <v>3.875</v>
+      </c>
+      <c r="D1375">
+        <v>0</v>
+      </c>
+      <c r="E1375">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:5">
+      <c r="A1376" s="1">
+        <v>47801</v>
+      </c>
+      <c r="B1376">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1376">
+        <v>3.875</v>
+      </c>
+      <c r="D1376">
+        <v>0</v>
+      </c>
+      <c r="E1376">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:5">
+      <c r="A1377" s="1">
+        <v>47982</v>
+      </c>
+      <c r="B1377">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1377">
+        <v>3.875</v>
+      </c>
+      <c r="D1377">
+        <v>0</v>
+      </c>
+      <c r="E1377">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:5">
+      <c r="A1378" s="1">
+        <v>48166</v>
+      </c>
+      <c r="B1378">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1378">
+        <v>3.875</v>
+      </c>
+      <c r="D1378">
+        <v>0</v>
+      </c>
+      <c r="E1378">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:5">
+      <c r="A1379" s="1">
+        <v>48348</v>
+      </c>
+      <c r="B1379">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1379">
+        <v>3.875</v>
+      </c>
+      <c r="D1379">
+        <v>0</v>
+      </c>
+      <c r="E1379">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:5">
+      <c r="A1380" s="1">
+        <v>48533</v>
+      </c>
+      <c r="B1380">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1380">
+        <v>3.875</v>
+      </c>
+      <c r="D1380">
+        <v>0</v>
+      </c>
+      <c r="E1380">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:5">
+      <c r="A1381" s="1">
+        <v>48715</v>
+      </c>
+      <c r="B1381">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1381">
+        <v>3.875</v>
+      </c>
+      <c r="D1381">
+        <v>0</v>
+      </c>
+      <c r="E1381">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:5">
+      <c r="A1382" s="1">
+        <v>48897</v>
+      </c>
+      <c r="B1382">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1382">
+        <v>3.875</v>
+      </c>
+      <c r="D1382">
+        <v>0</v>
+      </c>
+      <c r="E1382">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:5">
+      <c r="A1383" s="1">
+        <v>49079</v>
+      </c>
+      <c r="B1383">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1383">
+        <v>3.875</v>
+      </c>
+      <c r="D1383">
+        <v>0</v>
+      </c>
+      <c r="E1383">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:5">
+      <c r="A1384" s="1">
+        <v>49262</v>
+      </c>
+      <c r="B1384">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1384">
+        <v>3.875</v>
+      </c>
+      <c r="D1384">
+        <v>0</v>
+      </c>
+      <c r="E1384">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:5">
+      <c r="A1385" s="1">
+        <v>49443</v>
+      </c>
+      <c r="B1385">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1385">
+        <v>3.875</v>
+      </c>
+      <c r="D1385">
+        <v>0</v>
+      </c>
+      <c r="E1385">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:5">
+      <c r="A1386" s="1">
+        <v>49627</v>
+      </c>
+      <c r="B1386">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1386">
+        <v>3.875</v>
+      </c>
+      <c r="D1386">
+        <v>0</v>
+      </c>
+      <c r="E1386">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:5">
+      <c r="A1387" s="1">
+        <v>49809</v>
+      </c>
+      <c r="B1387">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1387">
+        <v>3.875</v>
+      </c>
+      <c r="D1387">
+        <v>0</v>
+      </c>
+      <c r="E1387">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:5">
+      <c r="A1388" s="1">
+        <v>49993</v>
+      </c>
+      <c r="B1388">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1388">
+        <v>3.875</v>
+      </c>
+      <c r="D1388">
+        <v>0</v>
+      </c>
+      <c r="E1388">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:5">
+      <c r="A1389" s="1">
+        <v>50174</v>
+      </c>
+      <c r="B1389">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1389">
+        <v>3.875</v>
+      </c>
+      <c r="D1389">
+        <v>0</v>
+      </c>
+      <c r="E1389">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:5">
+      <c r="A1390" s="1">
+        <v>50360</v>
+      </c>
+      <c r="B1390">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1390">
+        <v>3.875</v>
+      </c>
+      <c r="D1390">
+        <v>100</v>
+      </c>
+      <c r="E1390">
+        <f t="shared" si="0"/>
+        <v>103.875</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:5">
+      <c r="A1391" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1391">
+        <v>2</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:5">
+      <c r="A1392" s="1">
+        <v>45979</v>
+      </c>
+      <c r="E1392">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:5">
+      <c r="A1393" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1393">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1393">
+        <v>4.0625</v>
+      </c>
+      <c r="D1393">
+        <v>0</v>
+      </c>
+      <c r="E1393">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:5">
+      <c r="A1394" s="1">
+        <v>46344</v>
+      </c>
+      <c r="B1394">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1394">
+        <v>4.0625</v>
+      </c>
+      <c r="D1394">
+        <v>0</v>
+      </c>
+      <c r="E1394">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:5">
+      <c r="A1395" s="1">
+        <v>46525</v>
+      </c>
+      <c r="B1395">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1395">
+        <v>4.0625</v>
+      </c>
+      <c r="D1395">
+        <v>0</v>
+      </c>
+      <c r="E1395">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:5">
+      <c r="A1396" s="1">
+        <v>46709</v>
+      </c>
+      <c r="B1396">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1396">
+        <v>4.0625</v>
+      </c>
+      <c r="D1396">
+        <v>0</v>
+      </c>
+      <c r="E1396">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:5">
+      <c r="A1397" s="1">
+        <v>46891</v>
+      </c>
+      <c r="B1397">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1397">
+        <v>4.0625</v>
+      </c>
+      <c r="D1397">
+        <v>0</v>
+      </c>
+      <c r="E1397">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:5">
+      <c r="A1398" s="1">
+        <v>47077</v>
+      </c>
+      <c r="B1398">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1398">
+        <v>4.0625</v>
+      </c>
+      <c r="D1398">
+        <v>0</v>
+      </c>
+      <c r="E1398">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:5">
+      <c r="A1399" s="1">
+        <v>47256</v>
+      </c>
+      <c r="B1399">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1399">
+        <v>4.0625</v>
+      </c>
+      <c r="D1399">
+        <v>0</v>
+      </c>
+      <c r="E1399">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:5">
+      <c r="A1400" s="1">
+        <v>47441</v>
+      </c>
+      <c r="B1400">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1400">
+        <v>4.0625</v>
+      </c>
+      <c r="D1400">
+        <v>0</v>
+      </c>
+      <c r="E1400">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:5">
+      <c r="A1401" s="1">
+        <v>47623</v>
+      </c>
+      <c r="B1401">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1401">
+        <v>4.0625</v>
+      </c>
+      <c r="D1401">
+        <v>0</v>
+      </c>
+      <c r="E1401">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:5">
+      <c r="A1402" s="1">
+        <v>47805</v>
+      </c>
+      <c r="B1402">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1402">
+        <v>4.0625</v>
+      </c>
+      <c r="D1402">
+        <v>0</v>
+      </c>
+      <c r="E1402">
+        <f t="shared" si="0"/>
+        <v>4.0625</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:5">
+      <c r="A1403" s="1">
+        <v>47987</v>
+      </c>
+      <c r="B1403">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C1403">
+        <v>4.0625</v>
+      </c>
+      <c r="D1403">
+        <v>100</v>
+      </c>
+      <c r="E1403">
+        <f t="shared" si="0"/>
+        <v>104.0625</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:5">
+      <c r="A1404" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1404">
+        <v>2</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:5">
+      <c r="A1405" s="1">
+        <v>45981</v>
+      </c>
+      <c r="E1405">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:5">
+      <c r="A1406" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B1406">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1406">
+        <v>3.875</v>
+      </c>
+      <c r="D1406">
+        <v>0</v>
+      </c>
+      <c r="E1406">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:5">
+      <c r="A1407" s="1">
+        <v>46346</v>
+      </c>
+      <c r="B1407">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1407">
+        <v>3.875</v>
+      </c>
+      <c r="D1407">
+        <v>0</v>
+      </c>
+      <c r="E1407">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:5">
+      <c r="A1408" s="1">
+        <v>46527</v>
+      </c>
+      <c r="B1408">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1408">
+        <v>3.875</v>
+      </c>
+      <c r="D1408">
+        <v>0</v>
+      </c>
+      <c r="E1408">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:5">
+      <c r="A1409" s="1">
+        <v>46713</v>
+      </c>
+      <c r="B1409">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1409">
+        <v>3.875</v>
+      </c>
+      <c r="D1409">
+        <v>0</v>
+      </c>
+      <c r="E1409">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:5">
+      <c r="A1410" s="1">
+        <v>46895</v>
+      </c>
+      <c r="B1410">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1410">
+        <v>3.875</v>
+      </c>
+      <c r="D1410">
+        <v>0</v>
+      </c>
+      <c r="E1410">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:5">
+      <c r="A1411" s="1">
+        <v>47077</v>
+      </c>
+      <c r="B1411">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1411">
+        <v>3.875</v>
+      </c>
+      <c r="D1411">
+        <v>0</v>
+      </c>
+      <c r="E1411">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:5">
+      <c r="A1412" s="1">
+        <v>47259</v>
+      </c>
+      <c r="B1412">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1412">
+        <v>3.875</v>
+      </c>
+      <c r="D1412">
+        <v>0</v>
+      </c>
+      <c r="E1412">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:5">
+      <c r="A1413" s="1">
+        <v>47442</v>
+      </c>
+      <c r="B1413">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1413">
+        <v>3.875</v>
+      </c>
+      <c r="D1413">
+        <v>0</v>
+      </c>
+      <c r="E1413">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:5">
+      <c r="A1414" s="1">
+        <v>47623</v>
+      </c>
+      <c r="B1414">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1414">
+        <v>3.875</v>
+      </c>
+      <c r="D1414">
+        <v>0</v>
+      </c>
+      <c r="E1414">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:5">
+      <c r="A1415" s="1">
+        <v>47807</v>
+      </c>
+      <c r="B1415">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1415">
+        <v>3.875</v>
+      </c>
+      <c r="D1415">
+        <v>0</v>
+      </c>
+      <c r="E1415">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:5">
+      <c r="A1416" s="1">
+        <v>47988</v>
+      </c>
+      <c r="B1416">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1416">
+        <v>3.875</v>
+      </c>
+      <c r="D1416">
+        <v>0</v>
+      </c>
+      <c r="E1416">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:5">
+      <c r="A1417" s="1">
+        <v>48172</v>
+      </c>
+      <c r="B1417">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1417">
+        <v>3.875</v>
+      </c>
+      <c r="D1417">
+        <v>0</v>
+      </c>
+      <c r="E1417">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:5">
+      <c r="A1418" s="1">
+        <v>48354</v>
+      </c>
+      <c r="B1418">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1418">
+        <v>3.875</v>
+      </c>
+      <c r="D1418">
+        <v>0</v>
+      </c>
+      <c r="E1418">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:5">
+      <c r="A1419" s="1">
+        <v>48540</v>
+      </c>
+      <c r="B1419">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1419">
+        <v>3.875</v>
+      </c>
+      <c r="D1419">
+        <v>0</v>
+      </c>
+      <c r="E1419">
+        <f t="shared" si="0"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:5">
+      <c r="A1420" s="1">
+        <v>48719</v>
+      </c>
+      <c r="B1420">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1420">
+        <v>3.875</v>
+      </c>
+      <c r="D1420">
+        <v>0</v>
+      </c>
+      <c r="E1420">
+        <f t="shared" ref="E1420:E1425" si="1">+C1420+D1420</f>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:5">
+      <c r="A1421" s="1">
+        <v>48904</v>
+      </c>
+      <c r="B1421">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1421">
+        <v>3.875</v>
+      </c>
+      <c r="D1421">
+        <v>0</v>
+      </c>
+      <c r="E1421">
+        <f t="shared" si="1"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:5">
+      <c r="A1422" s="1">
+        <v>49086</v>
+      </c>
+      <c r="B1422">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1422">
+        <v>3.875</v>
+      </c>
+      <c r="D1422">
+        <v>0</v>
+      </c>
+      <c r="E1422">
+        <f t="shared" si="1"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:5">
+      <c r="A1423" s="1">
+        <v>49268</v>
+      </c>
+      <c r="B1423">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1423">
+        <v>3.875</v>
+      </c>
+      <c r="D1423">
+        <v>0</v>
+      </c>
+      <c r="E1423">
+        <f t="shared" si="1"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:5">
+      <c r="A1424" s="1">
+        <v>49450</v>
+      </c>
+      <c r="B1424">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1424">
+        <v>3.875</v>
+      </c>
+      <c r="D1424">
+        <v>0</v>
+      </c>
+      <c r="E1424">
+        <f t="shared" si="1"/>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:5">
+      <c r="A1425" s="1">
+        <v>49633</v>
+      </c>
+      <c r="B1425">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="C1425">
+        <v>3.875</v>
+      </c>
+      <c r="D1425">
+        <v>100</v>
+      </c>
+      <c r="E1425">
+        <f t="shared" si="1"/>
+        <v>103.875</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B312 B2 B21 B42 B73 B109 B152 B205 B224 B245 B276 B355 B367 B388 B396 B408 B414 B421 B427 B435 B445 B456 B466 B482 B490 B498 B503 B510 B520 B526 B534 B541 B549 B559 B569 B581 B589 B600 B616 B626 B636 B642 B652 B659 B673 B681 B691 B699 B709 B715 B727 B741 B749 B755 B767 B776 B782 B790 B794 B798 B808 B818 B832 B840 B855 B874 B885 B901 B917 B958 B970 B984 B998 B1014 B1030 B1040 B1058 B1082 B1104 B1126 B1148 B1172 B1191 B1219 B1235 B1253 B1271 B1291 B1307 B1325 B1335" xr:uid="{BD1BD003-9C46-4FBD-99EA-FC0DAEFD6ABE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B312 B2 B21 B42 B73 B109 B152 B205 B224 B245 B276 B355 B367 B388 B396 B408 B414 B421 B427 B435 B445 B456 B466 B482 B490 B498 B503 B510 B520 B526 B534 B541 B549 B559 B569 B581 B589 B600 B616 B626 B636 B642 B652 B659 B673 B681 B691 B699 B709 B715 B727 B741 B749 B755 B767 B776 B782 B790 B794 B798 B808 B818 B832 B840 B855 B874 B885 B901 B917 B958 B970 B984 B998 B1014 B1030 B1040 B1058 B1082 B1104 B1126 B1148 B1172 B1191 B1219 B1235 B1253 B1271 B1291 B1307 B1325 B1335 B1353 B1365 B1391 B1404" xr:uid="{BD1BD003-9C46-4FBD-99EA-FC0DAEFD6ABE}">
       <formula1>$J$2:$J$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D312 D2 D21 D42 D73 D109 D152 D205 D224 D245 D276 D355 D367 D388 D396 D408 D414 D421 D427 D435 D445 D456 D466 D482 D490 D498 D503 D510 D520 D526 D534 D541 D549 D559 D569 D581 D589 D600 D616 D626 D636 D642 D652 D659 D673 D681 D691 D699 D709 D715 D727 D741 D749 D755 D767 D776 D782 D790 D794 D798 D808 D818 D832 D840 D855 D874 D885 D901 D917 D958 D970 D984 D998 D1014 D1030 D1040 D1058 D1082 D1104 D1126 D1148 D1172 D1191 D1219 D1235 D1253 D1271 D1291 D1307 D1325 D1335" xr:uid="{48BF8691-1E10-4296-BB76-1715A86B19C5}">

--- a/bonos_flujos.xlsx
+++ b/bonos_flujos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64E288F3-120C-4729-9691-2657A1C7CB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D59DA2BE-1859-433A-B26E-2BC3FA2A549A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="195">
   <si>
     <t>GD29</t>
   </si>
@@ -23716,7 +23716,10 @@
       <c r="C1353">
         <v>2</v>
       </c>
-      <c r="D1353" t="s">
+      <c r="D1353" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1353" t="s">
         <v>188</v>
       </c>
     </row>
@@ -23915,7 +23918,10 @@
       <c r="C1365">
         <v>2</v>
       </c>
-      <c r="D1365" t="s">
+      <c r="D1365" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1365" t="s">
         <v>190</v>
       </c>
     </row>
@@ -24370,7 +24376,10 @@
       <c r="C1391">
         <v>2</v>
       </c>
-      <c r="D1391" t="s">
+      <c r="D1391" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1391" t="s">
         <v>192</v>
       </c>
     </row>
@@ -24592,6 +24601,9 @@
         <v>2</v>
       </c>
       <c r="D1404" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1404" t="s">
         <v>194</v>
       </c>
     </row>
@@ -24969,7 +24981,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B312 B2 B21 B42 B73 B109 B152 B205 B224 B245 B276 B355 B367 B388 B396 B408 B414 B421 B427 B435 B445 B456 B466 B482 B490 B498 B503 B510 B520 B526 B534 B541 B549 B559 B569 B581 B589 B600 B616 B626 B636 B642 B652 B659 B673 B681 B691 B699 B709 B715 B727 B741 B749 B755 B767 B776 B782 B790 B794 B798 B808 B818 B832 B840 B855 B874 B885 B901 B917 B958 B970 B984 B998 B1014 B1030 B1040 B1058 B1082 B1104 B1126 B1148 B1172 B1191 B1219 B1235 B1253 B1271 B1291 B1307 B1325 B1335 B1353 B1365 B1391 B1404" xr:uid="{BD1BD003-9C46-4FBD-99EA-FC0DAEFD6ABE}">
       <formula1>$J$2:$J$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D312 D2 D21 D42 D73 D109 D152 D205 D224 D245 D276 D355 D367 D388 D396 D408 D414 D421 D427 D435 D445 D456 D466 D482 D490 D498 D503 D510 D520 D526 D534 D541 D549 D559 D569 D581 D589 D600 D616 D626 D636 D642 D652 D659 D673 D681 D691 D699 D709 D715 D727 D741 D749 D755 D767 D776 D782 D790 D794 D798 D808 D818 D832 D840 D855 D874 D885 D901 D917 D958 D970 D984 D998 D1014 D1030 D1040 D1058 D1082 D1104 D1126 D1148 D1172 D1191 D1219 D1235 D1253 D1271 D1291 D1307 D1325 D1335" xr:uid="{48BF8691-1E10-4296-BB76-1715A86B19C5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D312 D2 D21 D42 D73 D109 D152 D205 D224 D245 D276 D355 D367 D388 D396 D408 D414 D421 D427 D435 D445 D456 D466 D482 D490 D498 D503 D510 D520 D526 D534 D541 D549 D559 D569 D581 D589 D600 D616 D626 D636 D642 D652 D659 D673 D681 D691 D699 D709 D715 D727 D741 D749 D755 D767 D776 D782 D790 D794 D798 D808 D818 D832 D840 D855 D874 D885 D901 D917 D958 D970 D984 D998 D1014 D1030 D1040 D1058 D1082 D1104 D1126 D1148 D1172 D1191 D1219 D1235 D1253 D1271 D1291 D1307 D1325 D1335 D1353 D1365 D1391" xr:uid="{48BF8691-1E10-4296-BB76-1715A86B19C5}">
       <formula1>$J$7:$J$9</formula1>
     </dataValidation>
   </dataValidations>
